--- a/laporan_padel_dki_jakarta_2026-10-06.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-06.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rp148.000 - Rp348.999</t>
+          <t>Rp148.000 - Rp680.000</t>
         </is>
       </c>
     </row>
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.880.000</t>
+          <t>Rp14.480.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.681.000</t>
+          <t>Rp2.186.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.324.000</t>
+          <t>Rp2.444.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp225.000</t>
+          <t>Rp545.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.325.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.690.000</t>
+          <t>Rp1.790.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp100.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.620.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.584.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.479.000</t>
+          <t>Rp2.482.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp1.393.000</t>
+          <t>Rp1.194.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp297.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.330.000</t>
+          <t>Rp5.195.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.675.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp1.924.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.773.000</t>
+          <t>Rp1.598.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.105.000</t>
+          <t>Rp3.915.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.445.000</t>
+          <t>Rp2.055.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp110.000</t>
+          <t>Rp75.000 - Rp110.000</t>
         </is>
       </c>
     </row>
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp716.000</t>
+          <t>Rp169.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.150.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp4.158.000</t>
+          <t>Rp4.338.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>76</v>
       </c>
       <c r="D65" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp8.260.000</t>
+          <t>Rp8.610.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp320.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.390.000</t>
+          <t>Rp4.110.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.710.000</t>
+          <t>Rp8.945.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp168.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp795.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.535.000</t>
+          <t>Rp9.785.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6711,21 +6711,21 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.460.000</t>
+          <t>Rp15.910.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6956,19 +6956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.900.000</t>
+          <t>Rp21.700.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.612.000</t>
+          <t>Rp6.762.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.105.000</t>
+          <t>Rp3.255.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp21.900.000</t>
+          <t>Rp22.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.330.000</t>
+          <t>Rp4.180.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rp135.000 - Rp200.000</t>
+          <t>Rp135.000 - Rp185.000</t>
         </is>
       </c>
     </row>
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp6.079.000</t>
+          <t>Rp6.378.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.095.000</t>
+          <t>Rp7.755.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.727.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp588.000</t>
+          <t>Rp338.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-06.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-06.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.340.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.960.000</t>
+          <t>Rp4.640.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.301.500</t>
+          <t>Rp11.635.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.114.000</t>
+          <t>Rp3.262.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.005.000</t>
+          <t>Rp1.515.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.660.000</t>
+          <t>Rp1.870.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.675.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp7.620.000</t>
+          <t>Rp7.840.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp585.000</t>
+          <t>Rp245.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.670.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.482.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.640.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.335.000</t>
+          <t>Rp1.435.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.010.000</t>
+          <t>Rp6.405.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp12.650.000</t>
+          <t>Rp12.550.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.055.000</t>
+          <t>Rp1.860.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.440.000</t>
+          <t>Rp4.790.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.588.000</t>
+          <t>Rp2.990.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp71.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.340.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp510.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp9.150.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.489.000</t>
+          <t>Rp1.669.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp168.000</t>
+          <t>Rp336.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp795.000</t>
+          <t>Rp497.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.785.000</t>
+          <t>Rp9.965.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.910.000</t>
+          <t>Rp14.760.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.775.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.700.000</t>
+          <t>Rp22.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.762.000</t>
+          <t>Rp6.438.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp12.025.000</t>
+          <t>Rp12.270.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.625.000</t>
+          <t>Rp10.725.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.296.000</t>
+          <t>Rp4.584.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp9.210.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.285.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.099.992</t>
+          <t>Rp4.349.992</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.727.000</t>
+          <t>Rp2.777.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp225.000 - Rp300.000</t>
+          <t>Rp175.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -9242,16 +9242,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-06.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-06.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.887.000</t>
+          <t>Rp2.187.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp6.525.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.255.000</t>
+          <t>Rp8.505.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.635.500</t>
+          <t>Rp11.616.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.624.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>170</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.600.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.776.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.480.000</t>
+          <t>Rp14.785.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp876.000</t>
+          <t>Rp1.252.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.186.000</t>
+          <t>Rp2.984.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.686.000</t>
+          <t>Rp1.886.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.445.000</t>
+          <t>Rp2.835.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.262.000</t>
+          <t>Rp3.606.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>84</v>
       </c>
       <c r="D51" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp349.000</t>
+          <t>Rp1.945.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp5.760.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.515.000</t>
+          <t>Rp1.695.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.870.000</t>
+          <t>Rp1.520.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp7.840.000</t>
+          <t>Rp7.940.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.773.000</t>
+          <t>Rp7.576.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp5.337.500</t>
+          <t>Rp4.837.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp245.000</t>
+          <t>Rp735.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.870.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.090.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.175.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.278.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp1.788.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>135</v>
       </c>
       <c r="D85" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp3.830.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.435.000</t>
+          <t>Rp2.305.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.195.000</t>
+          <t>Rp5.395.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.825.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp12.550.000</t>
+          <t>Rp14.350.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.915.000</t>
+          <t>Rp5.940.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.790.000</t>
+          <t>Rp5.140.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp15.600.000</t>
+          <t>Rp16.800.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.025.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp8.695.000</t>
+          <t>Rp9.575.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp230.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp10.050.000</t>
+          <t>Rp10.450.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp4.338.000</t>
+          <t>Rp4.635.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp9.600.000</t>
+          <t>Rp12.250.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D69" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp16.050.000</t>
+          <t>Rp16.600.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.280.000</t>
+          <t>Rp16.500.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp37.100.000</t>
+          <t>Rp38.300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp5.210.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp1.669.000</t>
+          <t>Rp2.319.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp7.600.000</t>
+          <t>Rp8.010.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp9.965.000</t>
+          <t>Rp10.355.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.499.000</t>
+          <t>Rp8.791.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp14.376.000</t>
+          <t>Rp14.931.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.760.000</t>
+          <t>Rp15.035.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.251.000</t>
+          <t>Rp2.789.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.800.000</t>
+          <t>Rp23.100.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.270.000</t>
+          <t>Rp6.770.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.255.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp4.040.000</t>
+          <t>Rp4.260.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.505.000</t>
+          <t>Rp2.645.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.725.000</t>
+          <t>Rp14.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.584.000</t>
+          <t>Rp5.248.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp22.500.000</t>
+          <t>Rp27.700.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.180.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.279.000</t>
+          <t>Rp1.799.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp6.378.000</t>
+          <t>Rp6.677.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp3.180.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp705.000</t>
+          <t>Rp1.075.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.274.988</t>
+          <t>Rp4.524.988</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.376.000</t>
+          <t>Rp3.726.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.800.000</t>
+          <t>Rp18.760.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp2.835.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.630.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.349.992</t>
+          <t>Rp4.474.992</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.425.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp290.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.095.000</t>
+          <t>Rp1.895.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.170.000</t>
+          <t>Rp2.555.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.055.000</t>
+          <t>Rp4.254.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.060.000</t>
+          <t>Rp3.310.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp338.000</t>
+          <t>Rp1.014.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp250.000</t>
+          <t>Rp175.000 - Rp300.000</t>
         </is>
       </c>
     </row>

--- a/laporan_padel_dki_jakarta_2026-10-06.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-06.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.616.500</t>
+          <t>Rp11.694.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.984.000</t>
+          <t>Rp2.184.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp4.785.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp8.100.000</t>
+          <t>Rp8.350.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp1.390.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp248.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.837.500</t>
+          <t>Rp5.337.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp3.980.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.940.000</t>
+          <t>Rp7.155.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp169.000</t>
+          <t>Rp358.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp9.050.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D69" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp16.600.000</t>
+          <t>Rp17.700.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.500.000</t>
+          <t>Rp13.585.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.150.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.210.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp8.010.000</t>
+          <t>Rp8.090.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.825.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp23.100.000</t>
+          <t>Rp23.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp570.000</t>
+          <t>Rp855.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp21.825.000</t>
+          <t>Rp22.025.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp2.820.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.075.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.115.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.910.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.630.000</t>
+          <t>Rp4.020.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.474.992</t>
+          <t>Rp4.724.992</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.895.000</t>
+          <t>Rp2.295.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp515.000</t>
+          <t>Rp885.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-06.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-06.xlsx
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.029.988</t>
+          <t>Rp4.733.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.785.000</t>
+          <t>Rp4.535.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp248.000</t>
+          <t>Rp347.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>80</v>
       </c>
       <c r="D81" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp3.278.000</t>
+          <t>Rp3.377.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.980.000</t>
+          <t>Rp14.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp497.000</t>
+          <t>Rp635.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.925.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp14.225.000</t>
+          <t>Rp14.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.524.988</t>
+          <t>Rp4.649.988</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.289.000</t>
+          <t>Rp2.439.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
